--- a/coaching_forms/029_productivity_coaching_intake_form--coaching_forms.xlsx
+++ b/coaching_forms/029_productivity_coaching_intake_form--coaching_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="41" customWidth="1" min="2" max="2"/>
+    <col width="41" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Preferred Communication Method</t>
+          <t>Preferred Communication Method Method</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>preferred_communication_method_method</t>
+          <t>preferred_communication_method_method_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Preferred Communication Method</t>
+          <t>Preferred Communication Method Method 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>preferred_communication_method_method</t>
+          <t>preferred_communication_method_method_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Preferred Communication Method</t>
+          <t>Preferred Communication Method Method 3</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -871,7 +871,7 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="47" customWidth="1" min="1" max="1"/>
+    <col width="49" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1083,7 +1083,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>preferred_communication_method_method_choices</t>
+          <t>preferred_communication_method_method_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1100,7 +1100,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>preferred_communication_method_method_choices</t>
+          <t>preferred_communication_method_method_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1117,7 +1117,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>preferred_communication_method_method_choices</t>
+          <t>preferred_communication_method_method_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1134,7 +1134,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>preferred_communication_method_method_choices</t>
+          <t>preferred_communication_method_method_3_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
